--- a/output/pdf_financials_xlsx/VET.xlsx
+++ b/output/pdf_financials_xlsx/VET.xlsx
@@ -7021,46 +7021,46 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-4.173</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-47.409</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>49.421</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>3.077</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-60.39</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>8.366</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.665</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-6.876</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-65.148</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-56.884</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>216.869</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-61.117</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-182.698</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="107">
@@ -7257,46 +7257,46 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>21.889</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>23.04</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>24.565</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>23.913</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>23.911</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>24.783</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>26.971</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>31.219</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>32.667</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>43.552</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>58.17</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>78.187</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>74.541</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>75.864</v>
       </c>
     </row>
     <row r="111">
@@ -7936,16 +7936,16 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-71.65900000000001</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-94.83799999999999</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-140.707</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-35.746</v>
       </c>
     </row>
     <row r="122">
@@ -8030,16 +8030,16 @@
         <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>347.284</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>196.387</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>138.341</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>202.617</v>
       </c>
       <c r="J123" s="3" t="n">
         <v>0</v>
@@ -8148,16 +8148,16 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>347.284</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>196.387</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>138.341</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>202.617</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -42878,7 +42878,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -43534,7 +43538,11 @@
           <t>Deferred tax recovery 13</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -43722,7 +43730,11 @@
           <t>Changes in non-cash operating working capital 21</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -45404,7 +45416,11 @@
           <t>Repurchase of shares 15</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -46408,7 +46424,11 @@
           <t>Accretion 9</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -47216,7 +47236,11 @@
           <t>Deferred tax recovery 12</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -47404,7 +47428,11 @@
           <t>Changes in non-cash operating working capital 20</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -48346,7 +48374,11 @@
           <t>Repurchase of shares 14</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -48994,7 +49026,11 @@
           <t>Accretion 8</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -49700,7 +49736,11 @@
           <t>Changes in non-cash operating working capital 19</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -50600,7 +50640,11 @@
           <t>Repurchase of shares 13</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -51436,7 +51480,11 @@
           <t>Deferred tax expense 11</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -56560,7 +56608,11 @@
           <t>Increase in long-term debt 12</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -58168,7 +58220,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -58812,7 +58868,11 @@
           <t>Changes in non-cash operating working capital 14</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -59454,7 +59514,11 @@
           <t>Increase in long-term debt 8</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr"/>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E546" t="inlineStr">
         <is>
           <t>-</t>
@@ -67498,7 +67562,11 @@
           <t>Changes in non-cash operating working capital 15</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr"/>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E631" t="inlineStr">
         <is>
           <t>-</t>
